--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8067" uniqueCount="899">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,7 +501,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Allergie in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -520,7 +520,7 @@
 </t>
   </si>
   <si>
-    <t>Status der Allergie; active | inactive | resolved</t>
+    <t>Status der Allergie; mögliche Codes: active | inactive | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the allergy or intolerance.</t>
@@ -543,7 +543,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>ToDo; Presumed, gibt es hierzu aktuelle Infos? kardinalität von clinicalStatus &amp; verificationStatus muss noch erarbeitet werden. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Allergie; mögliche Codes: unconfirmed | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -565,7 +565,7 @@
 Class</t>
   </si>
   <si>
-    <t>Identifikation ob es eine Allergie oder Intoleranz ist</t>
+    <t>Kennzeichnung, ob es sich um eine Allergie oder Intoleranz handelt.</t>
   </si>
   <si>
     <t>Identification of the underlying physiological mechanism for the reaction risk.</t>
@@ -587,7 +587,7 @@
 TypeReaction TypeClass</t>
   </si>
   <si>
-    <t>Differenzierung nach Kontext - Medikamente, Lebensmittel, Umwelt,.. - falls nur med. rele. dann ist es nicht notwendig, fachlich klären</t>
+    <t>ToDo - falls nur med. rele. dann ist es nicht notwendig, fachlich klären: Differenzierung nach Kontext z. B. Medikamente, Lebensmittel oder Umwelt.</t>
   </si>
   <si>
     <t>Category of the identified substance.</t>
@@ -609,7 +609,7 @@
 SeriousnessContra-indicationRisk</t>
   </si>
   <si>
-    <t>Einschätzung der Schwere (Anaphylaxie)</t>
+    <t>Einschätzung des Schweregrads, z. B. im Hinblick auf eine Anaphylaxie.</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
@@ -631,7 +631,7 @@
 </t>
   </si>
   <si>
-    <t>Allergiecode, Text verboten</t>
+    <t>Allergiecode; Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>Code for an allergy or intolerance statement (either a positive or a negated/excluded statement).  This may be a code for a substance or pharmaceutical product that is considered to be responsible for the adverse reaction risk (e.g., "Latex"), an allergy or intolerance condition (e.g., "Latex allergy"), or a negated/excluded code for a specific substance or class (e.g., "No latex allergy") or a general or categorical negated statement (e.g.,  "No known allergy", "No known drug allergies").  Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -735,7 +735,7 @@
 </t>
   </si>
   <si>
-    <t>Betroffene Person, auf die sich die Allergie bezieht</t>
+    <t>Betroffene Person, auf die sich die Allergie bezieht.</t>
   </si>
   <si>
     <t>The patient who has the allergy or intolerance.</t>
@@ -748,7 +748,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The encounter when the allergy or intolerance was asserted.</t>
@@ -761,7 +761,7 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>Erstes Aufzeichnungsdatum der Allergie(symptomatik)</t>
+    <t>Erstes Aufzeichnungsdatum der Allergie bzw. Allergiesymptomatik.</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -774,7 +774,7 @@
 </t>
   </si>
   <si>
-    <t>Dokumentationsdatum</t>
+    <t>Dokumentationsdatum.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
@@ -791,7 +791,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, die die Allergie ins System erfasst/dokumentiert</t>
+    <t>GDA, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Person (fachliche Quelle + related Person oder Patient selbst), die/der die Allergie bestätigt</t>
+    <t>Quelle der Information zur Allergie, z. B. Patient, behandelnde Person oder Dritter.</t>
   </si>
   <si>
     <t>The source of the information about the allergy that is recorded.</t>
@@ -820,7 +820,7 @@
     <t>AllergyIntolerance.lastOccurrence</t>
   </si>
   <si>
-    <t>Letztes Auftreten der Symptomatik - siehe manifestation</t>
+    <t>Letztes Auftreten der Symptomatik; siehe Manifestation.</t>
   </si>
   <si>
     <t>Represents the date and/or time of the last known occurrence of a reaction event.</t>
@@ -836,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen oder Freitext zur Allergie wird in reaction beschrieben</t>
+    <t>Zusätzliche Informationen; Freitext wird in reaction beschrieben.</t>
   </si>
   <si>
     <t>Additional narrative about the propensity for the Adverse Reaction, not captured in other fields.</t>
@@ -852,7 +852,7 @@
 </t>
   </si>
   <si>
-    <t>Details über die Allergiereaktion</t>
+    <t>Details zur allergischen Reaktion.</t>
   </si>
   <si>
     <t>Details about each adverse reaction event linked to exposure to the identified substance.</t>
@@ -874,7 +874,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitlicher Verlauf der Manifestation</t>
+    <t>Zeitlicher Verlauf der Manifestation.</t>
   </si>
   <si>
     <t>Zeitlicher Verlauf der Manifestation (&lt;6h, 6-24h, &gt;24h, unknown)</t>
@@ -900,7 +900,7 @@
     <t>AllergyIntolerance.reaction.substance</t>
   </si>
   <si>
-    <t>Spezifische Substanz die zur Allergie führt, wird in allergyintoleranz.code gelöst</t>
+    <t>Spezifische Substanz, die zur Allergie führt; wird über AllergyIntolerance.code abgebildet.</t>
   </si>
   <si>
     <t>Identification of the specific substance (or pharmaceutical product) considered to be responsible for the Adverse Reaction event. Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -922,7 +922,7 @@
 Signs</t>
   </si>
   <si>
-    <t>Aufgezeichnete klinische allergische Symptome</t>
+    <t>Aufgezeichnete klinische Symptome der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
@@ -944,7 +944,7 @@
 Text</t>
   </si>
   <si>
-    <t>Textbasierte Zusammenfassung der allergischen Reaktion</t>
+    <t>Textbasierte Zusammenfassung der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Text description about the reaction as a whole, including details of the manifestation if required.</t>
@@ -956,7 +956,7 @@
     <t>AllergyIntolerance.reaction.onset</t>
   </si>
   <si>
-    <t>Beginn der Reaktion</t>
+    <t>Beginn der Reaktion.</t>
   </si>
   <si>
     <t>Record of the date and/or time of the onset of the Reaction.</t>
@@ -965,7 +965,7 @@
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>Beschreibt ob die Reaktion mild, moderat,... war</t>
+    <t>Schweregrad der Reaktion, z. B. mild oder moderat.</t>
   </si>
   <si>
     <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
@@ -983,7 +983,7 @@
     <t>AllergyIntolerance.reaction.exposureRoute</t>
   </si>
   <si>
-    <t>Art der Exposition der betroffenen Person gegenüber der Substanz</t>
+    <t>Art der Exposition der betroffenen Person gegenüber der Substanz.</t>
   </si>
   <si>
     <t>Identification of the route by which the subject was exposed to the substance.</t>
@@ -1001,7 +1001,7 @@
     <t>AllergyIntolerance.reaction.note</t>
   </si>
   <si>
-    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation</t>
+    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional text about the adverse reaction event not captured in other fields.</t>
@@ -1127,7 +1127,7 @@
     <t>Condition.identifier</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -1139,8 +1139,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (wie:Status post), 
-mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
+    <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | recurrence | relapse | inactive | remission | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -1162,7 +1161,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Status der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>
@@ -1203,7 +1202,7 @@
     <t>Condition.severity</t>
   </si>
   <si>
-    <t>Schweregrad der Erkrankung</t>
+    <t>Schweregrad der Erkrankung.</t>
   </si>
   <si>
     <t>A subjective assessment of the severity of the condition as evaluated by the clinician.</t>
@@ -1222,7 +1221,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnosecode (Codierservice), Text verboten, Codesystem 1.SNOMED 2.Orphanet</t>
+    <t>Diagnosecode (Codierservice); Freitext ist nicht zulässig. Codesysteme: 1. SNOMED CT, 2. Orphanet.</t>
   </si>
   <si>
     <t>Identification of the condition, problem or diagnosis.</t>
@@ -1413,7 +1412,7 @@
     <t>Condition.bodySite</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose der Körper-Lokalisation</t>
+    <t>Zuordnung der Diagnose zu einer Körperstelle.</t>
   </si>
   <si>
     <t>The anatomical location where this condition manifests itself.</t>
@@ -1435,7 +1434,7 @@
 </t>
   </si>
   <si>
-    <t>Person, auf die sich die Diagnose bezieht</t>
+    <t>Person, auf die sich die Diagnose bezieht.</t>
   </si>
   <si>
     <t>Indicates the patient or group who the condition record is associated with.</t>
@@ -1456,7 +1455,7 @@
     <t>Condition.onset[x]</t>
   </si>
   <si>
-    <t>Beginn der Erkrankung/Diagnosezeitpunkt</t>
+    <t>Beginn der Erkrankung bzw. Diagnosezeitpunkt.</t>
   </si>
   <si>
     <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
@@ -1468,7 +1467,7 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>Ende der Erkrankung</t>
+    <t>Ende der Erkrankung.</t>
   </si>
   <si>
     <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
@@ -1484,7 +1483,7 @@
     <t>Condition.recordedDate</t>
   </si>
   <si>
-    <t>Zeitpunkt der Diagnosendokumentation</t>
+    <t>Zeitpunkt der Dokumentation der Diagnose.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
@@ -1493,13 +1492,13 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t>Ansonsten Gesundheitsdiensteanbieter, der die Diagnose eingetragen hat</t>
+    <t>GDA, der die Diagnose eingetragen hat.</t>
   </si>
   <si>
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t>Quelle der Information zur Diagnose (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Diagnose (z. B. behandelnde GDA, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the condition statement.</t>
@@ -1508,7 +1507,7 @@
     <t>Condition.stage</t>
   </si>
   <si>
-    <t>Stadium der Erkrankung</t>
+    <t>Stadium der Erkrankung.</t>
   </si>
   <si>
     <t>Clinical stage or grade of a condition. May include formal severity assessments.</t>
@@ -1577,7 +1576,7 @@
     <t>Condition.evidence</t>
   </si>
   <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz</t>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>Supporting evidence / manifestations that are the basis of the Condition's verification status, such as evidence that confirmed or refuted the condition.</t>
@@ -1634,7 +1633,7 @@
     <t>Condition.note</t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zur Diagnose als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional information about the Condition. This is a general notes/comments entry  for description of the Condition, its diagnosis and prognosis.</t>
@@ -1733,7 +1732,7 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner) {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference}
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
@@ -1860,7 +1859,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Liste.</t>
+    <t>Status der Liste.</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -1881,7 +1880,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt und hat daher den festen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -1982,8 +1981,8 @@
 </t>
   </si>
   <si>
-    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
-des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den Z-PI.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA ist sie eindeutig über den GDA-Index identifiziert und zum Zugriff auf die ELGA-Anwendung des Patienten berechtigt. 
+ Im Falle eines Patienten erfolgt die eindeutige Identifizierung über den Z-PI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -2074,7 +2073,7 @@
     <t>List.entry.deleted</t>
   </si>
   <si>
-    <t>Kennzeichnung, dass der Eintrag gelöscht wurde, ist nicht erlaubt (siehe Invariant lst-2).</t>
+    <t>Eine Kennzeichnung des Eintrags als gelöscht ist nicht zulässig (siehe Invariant list-emptyreason-required).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -2096,7 +2095,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird und das Datum der letzten Aktualisierung der Liste (List.date) dokumentiert wird.</t>
+    <t>Das Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird. Dokumentiert wird das Datum der letzten Aktualisierung der Liste (List.date).</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -2296,7 +2295,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
+    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll.</t>
   </si>
   <si>
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -2305,7 +2304,7 @@
     <t>Procedure.instantiatesUri</t>
   </si>
   <si>
-    <t>Verweis auf ein externes Dokument</t>
+    <t>Verweis auf ein externes Dokument.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -2325,7 +2324,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine Anforderung</t>
+    <t>Verweis auf eine Anforderung.</t>
   </si>
   <si>
     <t>A reference to a resource that contains details of the request for this procedure.</t>
@@ -2342,7 +2341,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
+    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource.</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -2354,7 +2353,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
+    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren.</t>
   </si>
   <si>
     <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
@@ -2374,7 +2373,7 @@
 Cancelled Reason</t>
   </si>
   <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
+    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -2392,7 +2391,7 @@
     <t>Procedure.category</t>
   </si>
   <si>
-    <t>Kategorisierung nach Verfahren</t>
+    <t>Kategorisierung nach Verfahren.</t>
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
@@ -2407,7 +2406,7 @@
     <t>Procedure.code</t>
   </si>
   <si>
-    <t>Prozedurencode der durchgeführten Prozedur</t>
+    <t>Prozedurencode der durchgeführten Prozedur.</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -2431,7 +2430,7 @@
     <t>Procedure.subject</t>
   </si>
   <si>
-    <t>Person, auf die sich die Prozedur bezieht</t>
+    <t>Person, auf die sich die Prozedur bezieht.</t>
   </si>
   <si>
     <t>The person, animal or group on which the procedure was performed.</t>
@@ -2449,7 +2448,7 @@
     <t>Procedure.performed[x]</t>
   </si>
   <si>
-    <t>Zeitpunkt der Durchführung</t>
+    <t>Zeitpunkt der Durchführung.</t>
   </si>
   <si>
     <t>Estimated or actual date, date-time, period, or age when the procedure was performed.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
@@ -2461,13 +2460,13 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen/dokumentiert hat</t>
+    <t>GDA, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Procedure.asserter</t>
   </si>
   <si>
-    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the procedure statement.</t>
@@ -2476,7 +2475,7 @@
     <t>Procedure.performer</t>
   </si>
   <si>
-    <t>Diese Person hat die Prozedur durchgeführt</t>
+    <t>Person, die die Prozedur durchgeführt hat.</t>
   </si>
   <si>
     <t>Limited to "real" people rather than equipment.</t>
@@ -2548,7 +2547,7 @@
 </t>
   </si>
   <si>
-    <t>Durchführungsort</t>
+    <t>Durchführungsort.</t>
   </si>
   <si>
     <t>The location where the procedure actually happened.  E.g. a newborn at home, a tracheostomy at a restaurant.</t>
@@ -2560,7 +2559,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Code, des med. Grundes für die Durchführung der Prozedur</t>
+    <t>Code des medizinischen Grundes für die Durchführung der Prozedur.</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -2582,7 +2581,7 @@
 </t>
   </si>
   <si>
-    <t>Begründung dass die Prozedur durchgeführt worden ist - Verweis auf eine andere R. wie Condition, Observation,...</t>
+    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie z.B. Condition oder Observation.</t>
   </si>
   <si>
     <t>The justification of why the procedure was performed.</t>
@@ -2595,7 +2594,7 @@
     <t>Procedure.bodySite</t>
   </si>
   <si>
-    <t>Betroffene Körperstelle</t>
+    <t>Betroffene Körperstelle.</t>
   </si>
   <si>
     <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
@@ -2607,7 +2606,7 @@
     <t>Procedure.outcome</t>
   </si>
   <si>
-    <t>Ergebnis der Prozedur</t>
+    <t>Ergebnis der Prozedur.</t>
   </si>
   <si>
     <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
@@ -2638,7 +2637,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Komplikation/en während dem Eingriff</t>
+    <t>Komplikation während dem Eingriff.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -2657,7 +2656,7 @@
 </t>
   </si>
   <si>
-    <t>Eine Diagnose die durch die durchgeführte Prozedur entstanden ist</t>
+    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -2669,7 +2668,7 @@
     <t>Procedure.followUp</t>
   </si>
   <si>
-    <t>Nachkontrolle (Code)</t>
+    <t>Nachkontrolle (Code).</t>
   </si>
   <si>
     <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
@@ -2684,7 +2683,7 @@
     <t>Procedure.note</t>
   </si>
   <si>
-    <t>Freitext zur Prozedur für Zusatzinformation</t>
+    <t>Freitext zur Prozedur als Zusatzinformation.</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -2708,7 +2707,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Prozedurendurchführendes Gerät</t>
+    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde.</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -2758,7 +2757,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf verwendete Materialien während der Prozedur (z.b. Medikamente)</t>
+    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente.</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
@@ -2773,7 +2772,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Code der Materialien, die während der Prozedur verwendetet wurden</t>
+    <t>Code der während der Prozedur verwendeten Materialien.</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>
@@ -2798,43 +2797,6 @@
   </si>
   <si>
     <t>element:AllergyIntolerance.reaction</t>
-  </si>
-  <si>
-    <t>at-elga-ediag-reference</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference</t>
-  </si>
-  <si>
-    <t>AtEdiagReference</t>
-  </si>
-  <si>
-    <t>AT ELGA e-Diagnose Reference</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Reference</t>
-  </si>
-  <si>
-    <t>AT e-Diagnose Reference</t>
-  </si>
-  <si>
-    <t>A reference from one resource to another.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Reference.id</t>
-  </si>
-  <si>
-    <t>Reference.extension</t>
   </si>
   <si>
     <t>at-elga-ediag-reported</t>
@@ -2980,7 +2942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -4084,7 +4046,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>898</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143">
@@ -4092,7 +4054,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>13</v>
+        <v>527</v>
       </c>
     </row>
     <row r="144">
@@ -4146,7 +4108,7 @@
         <v>24</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="151">
@@ -4182,7 +4144,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
     </row>
     <row r="156">
@@ -4190,7 +4152,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>900</v>
+        <v>529</v>
       </c>
     </row>
     <row r="157">
@@ -4210,181 +4172,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B159" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B166" s="2"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B173" s="2"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B174" s="2"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
+      <c r="A159" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="B181" t="s" s="2">
-        <v>910</v>
+      <c r="B159" t="s" s="2">
+        <v>898</v>
       </c>
     </row>
   </sheetData>
@@ -4394,7 +4186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK243"/>
+  <dimension ref="A1:AK236"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.57421875" customWidth="true" bestFit="true"/>
@@ -28596,10 +28388,10 @@
         <v>895</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28625,14 +28417,12 @@
         <v>79</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>901</v>
+        <v>138</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>903</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O232" s="2"/>
       <c r="P232" s="2"/>
       <c r="Q232" t="s" s="2">
         <v>23</v>
@@ -28681,7 +28471,7 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>77</v>
@@ -28693,7 +28483,7 @@
         <v>140</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>904</v>
+        <v>134</v>
       </c>
     </row>
     <row r="233">
@@ -28701,10 +28491,10 @@
         <v>895</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>905</v>
+        <v>534</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>905</v>
+        <v>534</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28804,21 +28594,21 @@
         <v>895</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>906</v>
+        <v>535</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>906</v>
+        <v>535</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>23</v>
@@ -28833,14 +28623,12 @@
         <v>128</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O234" s="2"/>
       <c r="P234" s="2"/>
       <c r="Q234" t="s" s="2">
         <v>23</v>
@@ -28909,10 +28697,10 @@
         <v>895</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>681</v>
+        <v>547</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>681</v>
+        <v>547</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28920,10 +28708,10 @@
       </c>
       <c r="F235" s="2"/>
       <c r="G235" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H235" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I235" t="s" s="2">
         <v>23</v>
@@ -28932,19 +28720,19 @@
         <v>23</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>678</v>
+        <v>544</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>679</v>
+        <v>545</v>
       </c>
       <c r="O235" t="s" s="2">
-        <v>680</v>
+        <v>546</v>
       </c>
       <c r="P235" s="2"/>
       <c r="Q235" t="s" s="2">
@@ -28952,7 +28740,7 @@
       </c>
       <c r="R235" s="2"/>
       <c r="S235" t="s" s="2">
-        <v>23</v>
+        <v>896</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>23</v>
@@ -28994,19 +28782,19 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>681</v>
+        <v>547</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI235" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>682</v>
+        <v>23</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236">
@@ -29014,10 +28802,10 @@
         <v>895</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29037,20 +28825,18 @@
         <v>23</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>99</v>
+        <v>428</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>684</v>
+        <v>551</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="O236" s="2"/>
       <c r="P236" s="2"/>
       <c r="Q236" t="s" s="2">
         <v>23</v>
@@ -29075,13 +28861,13 @@
         <v>23</v>
       </c>
       <c r="Y236" t="s" s="2">
-        <v>374</v>
+        <v>23</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>687</v>
+        <v>23</v>
       </c>
       <c r="AA236" t="s" s="2">
-        <v>688</v>
+        <v>23</v>
       </c>
       <c r="AB236" t="s" s="2">
         <v>23</v>
@@ -29099,7 +28885,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -29111,733 +28897,6 @@
         <v>23</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="D237" s="2"/>
-      <c r="E237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F237" s="2"/>
-      <c r="G237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="P237" s="2"/>
-      <c r="Q237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R237" s="2"/>
-      <c r="S237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK237" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="D238" s="2"/>
-      <c r="E238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F238" s="2"/>
-      <c r="G238" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H238" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K238" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L238" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N238" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O238" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="P238" s="2"/>
-      <c r="Q238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R238" s="2"/>
-      <c r="S238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG238" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AH238" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI238" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK238" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C239" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="D239" s="2"/>
-      <c r="E239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F239" s="2"/>
-      <c r="G239" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H239" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O239" s="2"/>
-      <c r="P239" s="2"/>
-      <c r="Q239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R239" s="2"/>
-      <c r="S239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG239" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AH239" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI239" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ239" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK239" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C240" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F240" s="2"/>
-      <c r="G240" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H240" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L240" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O240" s="2"/>
-      <c r="P240" s="2"/>
-      <c r="Q240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R240" s="2"/>
-      <c r="S240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG240" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AH240" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI240" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK240" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C241" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="E241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F241" s="2"/>
-      <c r="G241" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O241" s="2"/>
-      <c r="P241" s="2"/>
-      <c r="Q241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R241" s="2"/>
-      <c r="S241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C242" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="D242" s="2"/>
-      <c r="E242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F242" s="2"/>
-      <c r="G242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O242" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="P242" s="2"/>
-      <c r="Q242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R242" s="2"/>
-      <c r="S242" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C243" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="D243" s="2"/>
-      <c r="E243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F243" s="2"/>
-      <c r="G243" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O243" s="2"/>
-      <c r="P243" s="2"/>
-      <c r="Q243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R243" s="2"/>
-      <c r="S243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK243" t="s" s="2">
         <v>97</v>
       </c>
     </row>
